--- a/data/trans_orig/P33_1_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82648</t>
+          <t>80548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37020</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62456</t>
+          <t>62699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95837</t>
+          <t>95066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135055</t>
+          <t>135465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>365244</t>
+          <t>366869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399471</t>
+          <t>399896</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>235136</t>
+          <t>235973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>262460</t>
+          <t>263742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>611351</t>
+          <t>610927</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>656313</t>
+          <t>655099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25006</t>
+          <t>23814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24448</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>49405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76144</t>
+          <t>77356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79137</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>117766</t>
+          <t>117197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299112</t>
+          <t>298526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>328217</t>
+          <t>326477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>288907</t>
+          <t>287863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318294</t>
+          <t>318413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>596758</t>
+          <t>598037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>638612</t>
+          <t>638854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>32643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39688</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66371</t>
+          <t>66376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100412</t>
+          <t>100373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>25737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48193</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97611</t>
+          <t>101380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137920</t>
+          <t>141686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>414581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>450876</t>
+          <t>451985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109586</t>
+          <t>109831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132808</t>
+          <t>132798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>532678</t>
+          <t>531478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>576311</t>
+          <t>576051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>45933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75778</t>
+          <t>75548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38068</t>
+          <t>37513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70420</t>
+          <t>69817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104039</t>
+          <t>105576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185538</t>
+          <t>185526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237573</t>
+          <t>237204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104080</t>
+          <t>105677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142724</t>
+          <t>145486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300009</t>
+          <t>302403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365570</t>
+          <t>367603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>914718</t>
+          <t>919638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>972783</t>
+          <t>976414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>535279</t>
+          <t>534404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>577210</t>
+          <t>576262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1469367</t>
+          <t>1469949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1541750</t>
+          <t>1540631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>31208</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38013</t>
+          <t>37585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35181</t>
+          <t>35699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60404</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65603</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>94462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>133767</t>
+          <t>133577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>142078</t>
+          <t>143734</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191047</t>
+          <t>194147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>258332</t>
+          <t>257986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288853</t>
+          <t>287010</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>407206</t>
+          <t>407155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>448765</t>
+          <t>450182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>674578</t>
+          <t>672798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>726544</t>
+          <t>726406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75496</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52825</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>86632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264637</t>
+          <t>259166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322647</t>
+          <t>320306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269788</t>
+          <t>276278</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>333901</t>
+          <t>334402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260890</t>
+          <t>260606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>279156</t>
+          <t>279338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>855980</t>
+          <t>856251</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>919279</t>
+          <t>921333</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1127063</t>
+          <t>1127499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1194384</t>
+          <t>1192009</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118371</t>
+          <t>116769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>165895</t>
+          <t>165295</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>109735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>156019</t>
+          <t>155490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238867</t>
+          <t>238421</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>305122</t>
+          <t>303346</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>420415</t>
+          <t>420639</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>500996</t>
+          <t>498543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>630046</t>
+          <t>630463</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>720499</t>
+          <t>726235</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1072843</t>
+          <t>1072312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1192563</t>
+          <t>1192262</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2581307</t>
+          <t>2581887</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2667413</t>
+          <t>2667541</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2502467</t>
+          <t>2496776</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2602549</t>
+          <t>2596288</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5109629</t>
+          <t>5108938</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5239330</t>
+          <t>5242424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>32656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71287</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107412</t>
+          <t>104973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>44228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>73281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126458</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171169</t>
+          <t>174159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>312212</t>
+          <t>313976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>349020</t>
+          <t>351198</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>233748</t>
+          <t>236288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>264073</t>
+          <t>267211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>559327</t>
+          <t>557631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>607035</t>
+          <t>605411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76420</t>
+          <t>74543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>111928</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69965</t>
+          <t>69085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103514</t>
+          <t>102477</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>153297</t>
+          <t>154014</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>203931</t>
+          <t>206628</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290248</t>
+          <t>290525</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>328699</t>
+          <t>329467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224590</t>
+          <t>226004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259780</t>
+          <t>259631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>527652</t>
+          <t>526726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>578230</t>
+          <t>580259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48156</t>
+          <t>47649</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112595</t>
+          <t>114097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157804</t>
+          <t>157220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>82674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175528</t>
+          <t>176737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227736</t>
+          <t>229188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>432849</t>
+          <t>433296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>481419</t>
+          <t>481742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167320</t>
+          <t>166008</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196652</t>
+          <t>195972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613307</t>
+          <t>609592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668149</t>
+          <t>664367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>54629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88762</t>
+          <t>90811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40570</t>
+          <t>39188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78117</t>
+          <t>78745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117381</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219834</t>
+          <t>215290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>275136</t>
+          <t>271448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171976</t>
+          <t>172678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220680</t>
+          <t>222278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403155</t>
+          <t>403366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>477798</t>
+          <t>479334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>806888</t>
+          <t>806803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>867897</t>
+          <t>867625</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>516522</t>
+          <t>517432</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>568419</t>
+          <t>568632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1342750</t>
+          <t>1337734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421317</t>
+          <t>1418575</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55295</t>
+          <t>57678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32400</t>
+          <t>32809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60129</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>70234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108414</t>
+          <t>109411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84572</t>
+          <t>84142</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>121112</t>
+          <t>118943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>216808</t>
+          <t>216588</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>269464</t>
+          <t>268474</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>311906</t>
+          <t>313086</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378185</t>
+          <t>379269</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>345258</t>
+          <t>343845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>384632</t>
+          <t>383791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>446160</t>
+          <t>444811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>500712</t>
+          <t>500169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>799175</t>
+          <t>799415</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>871390</t>
+          <t>870135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>70673</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107263</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82637</t>
+          <t>82869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>120216</t>
+          <t>121283</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22202</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43791</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>286769</t>
+          <t>290409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>352791</t>
+          <t>351677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319583</t>
+          <t>320700</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>387281</t>
+          <t>385372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>206563</t>
+          <t>206474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231469</t>
+          <t>231846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662027</t>
+          <t>664011</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>728714</t>
+          <t>727121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>880009</t>
+          <t>880373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>951717</t>
+          <t>951164</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>165367</t>
+          <t>166687</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>224333</t>
+          <t>225728</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>157476</t>
+          <t>156620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208950</t>
+          <t>209384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>337065</t>
+          <t>340632</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>417976</t>
+          <t>418193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>642310</t>
+          <t>640958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>737754</t>
+          <t>740520</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>915174</t>
+          <t>911573</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1024372</t>
+          <t>1029303</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1592035</t>
+          <t>1585791</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1736122</t>
+          <t>1735289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2468423</t>
+          <t>2471922</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2576127</t>
+          <t>2579532</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2334682</t>
+          <t>2329612</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2446693</t>
+          <t>2448885</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4831804</t>
+          <t>4837660</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4988530</t>
+          <t>4992731</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>16512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>61178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97824</t>
+          <t>95270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78053</t>
+          <t>78693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117175</t>
+          <t>118089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162072</t>
+          <t>162037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>317001</t>
+          <t>317599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>352412</t>
+          <t>353888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>260452</t>
+          <t>259792</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>290331</t>
+          <t>291809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>589411</t>
+          <t>592197</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>637597</t>
+          <t>638221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>39573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63614</t>
+          <t>61872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97303</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51828</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83770</t>
+          <t>82988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>124857</t>
+          <t>126335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>166952</t>
+          <t>171463</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258472</t>
+          <t>260420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>294241</t>
+          <t>295661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>280322</t>
+          <t>279805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>312063</t>
+          <t>312012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550029</t>
+          <t>550032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>599206</t>
+          <t>596506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38793</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46178</t>
+          <t>46997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85057</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122312</t>
+          <t>122343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114714</t>
+          <t>114296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156072</t>
+          <t>157847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>369732</t>
+          <t>369398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409516</t>
+          <t>409776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110787</t>
+          <t>109094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133752</t>
+          <t>133934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>491637</t>
+          <t>487976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535706</t>
+          <t>536024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49454</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>82579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50317</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80518</t>
+          <t>79884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118462</t>
+          <t>118464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190135</t>
+          <t>192720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242749</t>
+          <t>248708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178955</t>
+          <t>179492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230717</t>
+          <t>229919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387085</t>
+          <t>382466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459821</t>
+          <t>458778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>837262</t>
+          <t>832320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>895842</t>
+          <t>895069</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>556605</t>
+          <t>556319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>608180</t>
+          <t>611728</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1408282</t>
+          <t>1411496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1489447</t>
+          <t>1491349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>28423</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52135</t>
+          <t>52827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83040</t>
+          <t>81379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81787</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119246</t>
+          <t>119432</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181521</t>
+          <t>181579</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>230151</t>
+          <t>229591</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>274020</t>
+          <t>275014</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>338760</t>
+          <t>335397</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458750</t>
+          <t>458735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>501805</t>
+          <t>500862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>480045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>531954</t>
+          <t>530617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>952831</t>
+          <t>955166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1020046</t>
+          <t>1018196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>61184</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99662</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>119188</t>
+          <t>118733</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38023</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240298</t>
+          <t>243829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>301239</t>
+          <t>299472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>266196</t>
+          <t>267775</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>330526</t>
+          <t>332190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>228862</t>
+          <t>229286</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>254258</t>
+          <t>253914</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696249</t>
+          <t>694971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>758903</t>
+          <t>758740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>934467</t>
+          <t>933991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1006207</t>
+          <t>1003677</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157192</t>
+          <t>156431</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>211290</t>
+          <t>208508</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>138700</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>190082</t>
+          <t>189832</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>307351</t>
+          <t>307062</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>381366</t>
+          <t>380964</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>555694</t>
+          <t>553621</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>649110</t>
+          <t>649943</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>789289</t>
+          <t>786314</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>894155</t>
+          <t>892703</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1372614</t>
+          <t>1367265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1511217</t>
+          <t>1512558</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2546660</t>
+          <t>2542455</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2646136</t>
+          <t>2646167</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2457788</t>
+          <t>2457982</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2570370</t>
+          <t>2572920</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5040063</t>
+          <t>5037975</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5187960</t>
+          <t>5191049</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93067</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132441</t>
+          <t>133705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98640</t>
+          <t>99227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130940</t>
+          <t>130225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>199374</t>
+          <t>202279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251115</t>
+          <t>250767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>360717</t>
+          <t>358394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>400107</t>
+          <t>398318</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303393</t>
+          <t>302981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>335512</t>
+          <t>334831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676263</t>
+          <t>675888</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>727052</t>
+          <t>723247</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82065</t>
+          <t>83411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>120189</t>
+          <t>120704</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86090</t>
+          <t>87071</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114135</t>
+          <t>116552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176052</t>
+          <t>176409</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>222208</t>
+          <t>220976</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>321773</t>
+          <t>322192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359366</t>
+          <t>359561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257875</t>
+          <t>254734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>286340</t>
+          <t>284951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>591637</t>
+          <t>593928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>638815</t>
+          <t>637866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>50058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215374</t>
+          <t>214637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>37558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55433</t>
+          <t>54821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75784</t>
+          <t>75909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258780</t>
+          <t>256263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>435759</t>
+          <t>434480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607444</t>
+          <t>607491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104018</t>
+          <t>104454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121981</t>
+          <t>122281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>548314</t>
+          <t>553894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>741776</t>
+          <t>743127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14291</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>30401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47732</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215353</t>
+          <t>214294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>276693</t>
+          <t>274653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304379</t>
+          <t>299710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>684837</t>
+          <t>703460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>525832</t>
+          <t>525274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1093368</t>
+          <t>1091159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>684482</t>
+          <t>685389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>747047</t>
+          <t>745426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>263162</t>
+          <t>243939</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>636537</t>
+          <t>640912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>816648</t>
+          <t>823090</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1372558</t>
+          <t>1374480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>33162</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44052</t>
+          <t>45159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>90317</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>129016</t>
+          <t>126073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>164600</t>
+          <t>164984</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>258537</t>
+          <t>259000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>277979</t>
+          <t>276405</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>373223</t>
+          <t>370960</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>315302</t>
+          <t>317761</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>354173</t>
+          <t>355252</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,47 +13076,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>69,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>561139</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>524997</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>626075</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>69,39%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>781</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>561139</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>522661</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>629623</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>69,39%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>855181</t>
+          <t>857153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>958644</t>
+          <t>960427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41569</t>
+          <t>41160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,47 +13341,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>30171</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>21962</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>41155</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>3,12%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>30171</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>21581</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>41394</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>45159</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153438</t>
+          <t>154400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>191097</t>
+          <t>191467</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173922</t>
+          <t>174462</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223864</t>
+          <t>222758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>190053</t>
+          <t>191138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>225316</t>
+          <t>224927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>508851</t>
+          <t>507085</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>549547</t>
+          <t>548256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>712603</t>
+          <t>714866</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>766084</t>
+          <t>766525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58470</t>
+          <t>56652</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97384</t>
+          <t>98198</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102757</t>
+          <t>102401</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>147342</t>
+          <t>145178</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>533799</t>
+          <t>486454</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>791550</t>
+          <t>788768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>933202</t>
+          <t>933105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1622933</t>
+          <t>1616391</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1610671</t>
+          <t>1607886</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2368251</t>
+          <t>2297626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2433971</t>
+          <t>2437276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2704761</t>
+          <t>2760795</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1793159</t>
+          <t>1791315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2456851</t>
+          <t>2459848</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4270088</t>
+          <t>4337272</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5019138</t>
+          <t>5025940</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50251</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80548</t>
+          <t>83674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62699</t>
+          <t>62011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95066</t>
+          <t>96393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135465</t>
+          <t>135561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>366869</t>
+          <t>365013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399896</t>
+          <t>401203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>235973</t>
+          <t>236249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263742</t>
+          <t>262911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>610927</t>
+          <t>612173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>655099</t>
+          <t>653684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23814</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25135</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49405</t>
+          <t>49933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48397</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>76123</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79456</t>
+          <t>80144</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>117197</t>
+          <t>119223</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>298526</t>
+          <t>298354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>326477</t>
+          <t>328353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287863</t>
+          <t>290107</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>318413</t>
+          <t>318405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>598037</t>
+          <t>596360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>638854</t>
+          <t>637659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18715</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66376</t>
+          <t>65726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100373</t>
+          <t>99765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48728</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101380</t>
+          <t>98447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141686</t>
+          <t>140882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>414581</t>
+          <t>412861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451985</t>
+          <t>449390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109831</t>
+          <t>109215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132798</t>
+          <t>131935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531478</t>
+          <t>533940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>576051</t>
+          <t>577983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45933</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75548</t>
+          <t>74310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>37744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69817</t>
+          <t>69443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105576</t>
+          <t>103000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185526</t>
+          <t>184104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237204</t>
+          <t>240754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105677</t>
+          <t>106573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145486</t>
+          <t>147372</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302403</t>
+          <t>297475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367603</t>
+          <t>366395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>919638</t>
+          <t>914830</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>976414</t>
+          <t>974989</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534404</t>
+          <t>531252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>576262</t>
+          <t>574808</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1469949</t>
+          <t>1468449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1540631</t>
+          <t>1543649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37585</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66433</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94462</t>
+          <t>94431</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>133577</t>
+          <t>133208</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>143734</t>
+          <t>144442</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194147</t>
+          <t>190270</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>257986</t>
+          <t>256093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>287010</t>
+          <t>286795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>407155</t>
+          <t>406051</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>450182</t>
+          <t>449135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>672798</t>
+          <t>673094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>726406</t>
+          <t>725448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44257</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>75273</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53109</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86632</t>
+          <t>86120</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>259166</t>
+          <t>262132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>320306</t>
+          <t>322788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>276278</t>
+          <t>272016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>334402</t>
+          <t>338887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260606</t>
+          <t>260379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>279338</t>
+          <t>279530</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>856251</t>
+          <t>856276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>921333</t>
+          <t>920023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1127499</t>
+          <t>1123331</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1192009</t>
+          <t>1194058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116769</t>
+          <t>119522</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>165295</t>
+          <t>166104</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>110747</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>155490</t>
+          <t>155247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238421</t>
+          <t>238602</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>303346</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>420639</t>
+          <t>419476</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498543</t>
+          <t>498916</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>630463</t>
+          <t>630036</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>726235</t>
+          <t>719774</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1072312</t>
+          <t>1074692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1192262</t>
+          <t>1196677</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2581887</t>
+          <t>2581476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2667541</t>
+          <t>2665998</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2496776</t>
+          <t>2498629</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2596288</t>
+          <t>2595739</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5108938</t>
+          <t>5101839</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5242424</t>
+          <t>5237043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104973</t>
+          <t>106367</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44228</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73281</t>
+          <t>74889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>125530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174159</t>
+          <t>170872</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313976</t>
+          <t>313538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>351198</t>
+          <t>352384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>236288</t>
+          <t>235983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>267211</t>
+          <t>264315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>557631</t>
+          <t>560073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>605411</t>
+          <t>607228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>15990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>36335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74543</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111928</t>
+          <t>111748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69085</t>
+          <t>70441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102477</t>
+          <t>104886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>154014</t>
+          <t>151334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>206628</t>
+          <t>203540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290525</t>
+          <t>293208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>329467</t>
+          <t>330254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>224075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259631</t>
+          <t>258945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526726</t>
+          <t>528698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>580259</t>
+          <t>582330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24417</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47649</t>
+          <t>50317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57823</t>
+          <t>58437</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114097</t>
+          <t>113924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157220</t>
+          <t>158785</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>53644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82674</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176737</t>
+          <t>174985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229188</t>
+          <t>228333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>433296</t>
+          <t>434107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>481742</t>
+          <t>481180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>164430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195972</t>
+          <t>195608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>609592</t>
+          <t>610890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>664367</t>
+          <t>666046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54629</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90811</t>
+          <t>88915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78745</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120892</t>
+          <t>118412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215290</t>
+          <t>215018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271448</t>
+          <t>273345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172678</t>
+          <t>171178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222278</t>
+          <t>221549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403366</t>
+          <t>403544</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>479334</t>
+          <t>476792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>806803</t>
+          <t>805127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>867625</t>
+          <t>869053</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>517432</t>
+          <t>517053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>568632</t>
+          <t>569753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1337734</t>
+          <t>1339637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1418575</t>
+          <t>1420716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31599</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57678</t>
+          <t>57132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60227</t>
+          <t>61479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70234</t>
+          <t>71808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109411</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84142</t>
+          <t>84068</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>118943</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>216588</t>
+          <t>216966</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>268474</t>
+          <t>269858</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>313086</t>
+          <t>310121</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>379269</t>
+          <t>373749</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>343845</t>
+          <t>345176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>383791</t>
+          <t>384820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>444811</t>
+          <t>446180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>500169</t>
+          <t>499972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>799415</t>
+          <t>805203</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>870135</t>
+          <t>873023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70673</t>
+          <t>70889</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>105434</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82869</t>
+          <t>81509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>121283</t>
+          <t>121432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>290409</t>
+          <t>290326</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>351677</t>
+          <t>351064</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>320700</t>
+          <t>319760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>385372</t>
+          <t>386100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>206474</t>
+          <t>207517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231846</t>
+          <t>231739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>664011</t>
+          <t>664488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>727121</t>
+          <t>727233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>880373</t>
+          <t>881381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>951164</t>
+          <t>951480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166687</t>
+          <t>166045</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>225728</t>
+          <t>224526</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>156620</t>
+          <t>155360</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>209384</t>
+          <t>209018</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340632</t>
+          <t>336460</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>418193</t>
+          <t>417148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>640958</t>
+          <t>640481</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>740520</t>
+          <t>738514</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>911573</t>
+          <t>916665</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1029303</t>
+          <t>1027038</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1585791</t>
+          <t>1588380</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1735289</t>
+          <t>1740109</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2471922</t>
+          <t>2470748</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2579532</t>
+          <t>2577937</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2329612</t>
+          <t>2334195</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2448885</t>
+          <t>2447148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4837660</t>
+          <t>4835294</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4992731</t>
+          <t>4993194</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61178</t>
+          <t>61390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95270</t>
+          <t>94911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48329</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78693</t>
+          <t>77471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118089</t>
+          <t>117683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162037</t>
+          <t>160726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>317599</t>
+          <t>318221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>353888</t>
+          <t>353016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>259792</t>
+          <t>261107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>291809</t>
+          <t>291974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>592197</t>
+          <t>590371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>638221</t>
+          <t>637004</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>18922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39573</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61872</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>97531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52351</t>
+          <t>52473</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82988</t>
+          <t>83678</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>123890</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>171463</t>
+          <t>171068</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260420</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>295661</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>279805</t>
+          <t>278394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>312012</t>
+          <t>312305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550032</t>
+          <t>548808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>596506</t>
+          <t>597911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>37052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>46834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84393</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122343</t>
+          <t>123702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114296</t>
+          <t>112846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157847</t>
+          <t>155380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>369398</t>
+          <t>368567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409776</t>
+          <t>408741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109094</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133934</t>
+          <t>133142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>487976</t>
+          <t>490775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536024</t>
+          <t>536498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>49524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82579</t>
+          <t>81472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47707</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79884</t>
+          <t>80428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118464</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192720</t>
+          <t>188864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>248708</t>
+          <t>246155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179492</t>
+          <t>179296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>229919</t>
+          <t>231006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382466</t>
+          <t>382723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>458778</t>
+          <t>454708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>832320</t>
+          <t>834274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>895069</t>
+          <t>893343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>556319</t>
+          <t>557005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>611728</t>
+          <t>610076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1411496</t>
+          <t>1413676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1491349</t>
+          <t>1493385</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,82%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28423</t>
+          <t>27807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52827</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>48320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81379</t>
+          <t>81899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82641</t>
+          <t>83109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119432</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181579</t>
+          <t>180272</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>229591</t>
+          <t>228276</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>275014</t>
+          <t>273731</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335397</t>
+          <t>336706</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458735</t>
+          <t>460196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>500862</t>
+          <t>500856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>480045</t>
+          <t>484251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>530617</t>
+          <t>533023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>955166</t>
+          <t>955022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1018196</t>
+          <t>1020938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>28006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61184</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96974</t>
+          <t>101144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>78067</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118733</t>
+          <t>117616</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17575</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>243829</t>
+          <t>242829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>299472</t>
+          <t>299634</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>267775</t>
+          <t>268543</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332190</t>
+          <t>332693</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>229286</t>
+          <t>229142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>253914</t>
+          <t>253958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694971</t>
+          <t>695405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>758740</t>
+          <t>759247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>933991</t>
+          <t>934739</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1003677</t>
+          <t>1004673</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156431</t>
+          <t>156950</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208508</t>
+          <t>210185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>136692</t>
+          <t>135905</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189832</t>
+          <t>188846</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>307062</t>
+          <t>308840</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>380964</t>
+          <t>382907</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>553621</t>
+          <t>554722</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>649943</t>
+          <t>642001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>786314</t>
+          <t>789222</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>892703</t>
+          <t>893909</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1367265</t>
+          <t>1364498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1512558</t>
+          <t>1507728</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2542455</t>
+          <t>2548673</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2646167</t>
+          <t>2647719</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2457982</t>
+          <t>2459329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2572920</t>
+          <t>2566475</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5037975</t>
+          <t>5043337</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5191049</t>
+          <t>5189039</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>112153</t>
+          <t>119555</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>100751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133705</t>
+          <t>141041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>113994</t>
+          <t>122888</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99227</t>
+          <t>105407</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130225</t>
+          <t>138655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>226147</t>
+          <t>242443</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202279</t>
+          <t>219000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250767</t>
+          <t>272634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>416727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>358394</t>
+          <t>395115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>398318</t>
+          <t>435907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>320436</t>
+          <t>351128</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>302981</t>
+          <t>334847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>334831</t>
+          <t>368717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>700645</t>
+          <t>767855</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>675888</t>
+          <t>735240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>723247</t>
+          <t>792280</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>495154</t>
+          <t>540079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>442082</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>442082</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>442082</t>
+          <t>482388</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>937236</t>
+          <t>1022467</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>937236</t>
+          <t>1022467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>937236</t>
+          <t>1022467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98568</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83411</t>
+          <t>85427</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>120704</t>
+          <t>122327</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100721</t>
+          <t>109925</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87071</t>
+          <t>94624</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116552</t>
+          <t>125829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>199289</t>
+          <t>212148</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176409</t>
+          <t>187118</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>220976</t>
+          <t>235976</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>343949</t>
+          <t>369277</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>322192</t>
+          <t>349874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359561</t>
+          <t>386363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>271370</t>
+          <t>300550</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>254734</t>
+          <t>284108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284951</t>
+          <t>316726</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>615320</t>
+          <t>669828</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>593928</t>
+          <t>647006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>637866</t>
+          <t>695688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>476661</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>476661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446835</t>
+          <t>476661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>415060</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>415060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>415060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>822553</t>
+          <t>891722</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822553</t>
+          <t>891722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>822553</t>
+          <t>891722</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>129687</t>
+          <t>141927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50058</t>
+          <t>123198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214637</t>
+          <t>162937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45727</t>
+          <t>49943</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37558</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>59439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>175414</t>
+          <t>191870</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75909</t>
+          <t>168051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256263</t>
+          <t>213149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>524027</t>
+          <t>312369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>434480</t>
+          <t>290829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607491</t>
+          <t>331637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113661</t>
+          <t>129708</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104454</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122281</t>
+          <t>140190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>637688</t>
+          <t>442077</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553894</t>
+          <t>419160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743127</t>
+          <t>465362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>462054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>462054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>659926</t>
+          <t>462054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>162164</t>
+          <t>182573</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>162164</t>
+          <t>182573</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162164</t>
+          <t>182573</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>822090</t>
+          <t>644627</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>822090</t>
+          <t>644627</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>822090</t>
+          <t>644627</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,17 +12374,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30401</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33978</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>27378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46377</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>241388</t>
+          <t>253009</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214294</t>
+          <t>226568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274653</t>
+          <t>286958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>447656</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299710</t>
+          <t>248493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>703460</t>
+          <t>297331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>689044</t>
+          <t>523709</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>525274</t>
+          <t>488795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1091159</t>
+          <t>561514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>718736</t>
+          <t>802647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>685389</t>
+          <t>769052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>745426</t>
+          <t>828849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>495400</t>
+          <t>551358</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>243939</t>
+          <t>527315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>640912</t>
+          <t>573848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1214136</t>
+          <t>1354004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>823090</t>
+          <t>1314556</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1374480</t>
+          <t>1391462</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>981345</t>
+          <t>1079001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>981345</t>
+          <t>1079001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>981345</t>
+          <t>1079001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>955812</t>
+          <t>836661</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>955812</t>
+          <t>836661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>955812</t>
+          <t>836661</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1937158</t>
+          <t>1915662</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1937158</t>
+          <t>1915662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1937158</t>
+          <t>1915662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33162</t>
+          <t>34858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>26259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45159</t>
+          <t>46636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>108426</t>
+          <t>129496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90317</t>
+          <t>108664</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126073</t>
+          <t>151012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>224342</t>
+          <t>247080</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>164984</t>
+          <t>226122</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>259000</t>
+          <t>268807</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>332768</t>
+          <t>376576</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>276405</t>
+          <t>350161</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>370960</t>
+          <t>408236</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>336422</t>
+          <t>408072</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>317761</t>
+          <t>385796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>355252</t>
+          <t>429997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>525564</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>524997</t>
+          <t>502281</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>626075</t>
+          <t>546627</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>897560</t>
+          <t>933635</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>857153</t>
+          <t>902074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>960427</t>
+          <t>962283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>454374</t>
+          <t>547674</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>454374</t>
+          <t>547674</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>454374</t>
+          <t>547674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>808674</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>808674</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>808674</t>
+          <t>797969</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1263048</t>
+          <t>1345643</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1263048</t>
+          <t>1345643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1263048</t>
+          <t>1345643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>48768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>50379</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45159</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>172647</t>
+          <t>191037</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154400</t>
+          <t>171427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>191467</t>
+          <t>213871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>195830</t>
+          <t>214616</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174462</t>
+          <t>189148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222758</t>
+          <t>242134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>213114</t>
+          <t>210039</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>191138</t>
+          <t>191754</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>224927</t>
+          <t>221715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>529446</t>
+          <t>587208</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>507085</t>
+          <t>563089</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>548256</t>
+          <t>609907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>742561</t>
+          <t>797247</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>714866</t>
+          <t>767651</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>766525</t>
+          <t>823808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>236297</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>236297</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>236297</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>732264</t>
+          <t>813434</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>732264</t>
+          <t>813434</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>732264</t>
+          <t>813434</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>968562</t>
+          <t>1047052</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>968562</t>
+          <t>1047052</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>968562</t>
+          <t>1047052</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>50168</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56652</t>
+          <t>64824</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>80177</t>
+          <t>90997</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98198</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>124246</t>
+          <t>141165</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102401</t>
+          <t>121268</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145178</t>
+          <t>167027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>713405</t>
+          <t>769788</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>486454</t>
+          <t>718906</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>788768</t>
+          <t>824846</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1105086</t>
+          <t>991574</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>933105</t>
+          <t>942756</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1616391</t>
+          <t>1038871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1818491</t>
+          <t>1761362</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1607886</t>
+          <t>1694648</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2297626</t>
+          <t>1831361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2516458</t>
+          <t>2519131</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2437276</t>
+          <t>2467331</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2760795</t>
+          <t>2573425</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2291453</t>
+          <t>2445515</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1791315</t>
+          <t>2397336</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2459848</t>
+          <t>2494032</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4807910</t>
+          <t>4964645</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4337272</t>
+          <t>4890479</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5025940</t>
+          <t>5031247</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>71,22%</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3273932</t>
+          <t>3339087</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3273932</t>
+          <t>3339087</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3273932</t>
+          <t>3339087</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3476715</t>
+          <t>3528085</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3476715</t>
+          <t>3528085</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3476715</t>
+          <t>3528085</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6750647</t>
+          <t>6867172</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6750647</t>
+          <t>6867172</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6750647</t>
+          <t>6867172</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
